--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.03417411253415</v>
+        <v>8.7805532932868</v>
       </c>
       <c r="D2" t="n">
-        <v>54.00612145874815</v>
+        <v>8.775994737046574</v>
       </c>
       <c r="E2" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F2" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.62904524894099</v>
+        <v>4.81471985295291</v>
       </c>
       <c r="D3" t="n">
-        <v>29.52193101571289</v>
+        <v>4.797313790053344</v>
       </c>
       <c r="E3" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F3" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.87758180710051</v>
+        <v>4.530107043653833</v>
       </c>
       <c r="D4" t="n">
-        <v>27.69016288486348</v>
+        <v>4.499651468790315</v>
       </c>
       <c r="E4" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F4" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.76808622971492</v>
+        <v>4.187314012328676</v>
       </c>
       <c r="D5" t="n">
-        <v>25.83838513581522</v>
+        <v>4.198737584569974</v>
       </c>
       <c r="E5" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F5" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.30416627891675</v>
+        <v>7.361927020323972</v>
       </c>
       <c r="D6" t="n">
-        <v>17.10263137648707</v>
+        <v>2.779177598679149</v>
       </c>
       <c r="E6" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F6" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.24921079788007</v>
+        <v>5.565496754655513</v>
       </c>
       <c r="D7" t="n">
-        <v>34.41731803540946</v>
+        <v>5.592814180754037</v>
       </c>
       <c r="E7" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F7" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.24702788377142</v>
+        <v>4.265142031112855</v>
       </c>
       <c r="D8" t="n">
-        <v>26.42685643038439</v>
+        <v>4.294364169937464</v>
       </c>
       <c r="E8" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F8" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.6688882314751</v>
+        <v>7.258694337614704</v>
       </c>
       <c r="D9" t="n">
-        <v>8.006954984574348</v>
+        <v>1.301130184993332</v>
       </c>
       <c r="E9" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F9" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.87145308945514</v>
+        <v>7.129111127036461</v>
       </c>
       <c r="D10" t="n">
-        <v>43.83226637195028</v>
+        <v>7.122743285441921</v>
       </c>
       <c r="E10" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F10" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.96275181708137</v>
+        <v>5.843947170275722</v>
       </c>
       <c r="D11" t="n">
-        <v>35.91803397984786</v>
+        <v>5.836680521725277</v>
       </c>
       <c r="E11" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F11" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.30881470516491</v>
+        <v>5.412682389589297</v>
       </c>
       <c r="D12" t="n">
-        <v>33.28209679120134</v>
+        <v>5.408340728570218</v>
       </c>
       <c r="E12" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F12" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.90886235034115</v>
+        <v>7.297690131930437</v>
       </c>
       <c r="D13" t="n">
-        <v>22.27666940994546</v>
+        <v>3.619958779116138</v>
       </c>
       <c r="E13" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F13" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.81611729790807</v>
+        <v>4.845119060910061</v>
       </c>
       <c r="D14" t="n">
-        <v>29.74150079371352</v>
+        <v>4.832993878978447</v>
       </c>
       <c r="E14" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F14" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.65245625673487</v>
+        <v>7.418524141719415</v>
       </c>
       <c r="D15" t="n">
-        <v>45.72875161536273</v>
+        <v>7.430922137496443</v>
       </c>
       <c r="E15" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F15" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>19.35109495463869</v>
+        <v>3.144552930128786</v>
       </c>
       <c r="D16" t="n">
-        <v>19.30025301281169</v>
+        <v>3.1362911145819</v>
       </c>
       <c r="E16" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F16" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>15.51978904835516</v>
+        <v>2.521965720357714</v>
       </c>
       <c r="D17" t="n">
-        <v>15.50427762560299</v>
+        <v>2.519445114160485</v>
       </c>
       <c r="E17" t="n">
-        <v>10.45352203580208</v>
+        <v>1.698697330817838</v>
       </c>
       <c r="F17" t="n">
-        <v>11.57100354234825</v>
+        <v>1.880288075631591</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
